--- a/resources/Programmes/programmeclasseCI.xlsx
+++ b/resources/Programmes/programmeclasseCI.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\colyl\Documents\Alymia\Gestion scolaire\Back\Gestion-Scolaire\resources\Programmes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\gestionscolaire\resources\Programmes\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9252"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7155"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="141">
   <si>
     <t>Matiere</t>
   </si>
@@ -450,6 +450,12 @@
   </si>
   <si>
     <t>NULL</t>
+  </si>
+  <si>
+    <t>heure_debut</t>
+  </si>
+  <si>
+    <t>heure_fin</t>
   </si>
 </sst>
 </file>
@@ -778,17 +784,21 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="18.33203125" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="18.21875" customWidth="1"/>
-    <col min="8" max="8" width="22.5546875" customWidth="1"/>
-    <col min="9" max="9" width="19.109375" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="8" max="10" width="22.5703125" customWidth="1"/>
+    <col min="11" max="11" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -814,10 +824,16 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>9</v>
       </c>
@@ -843,11 +859,19 @@
         <v>16</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
+    <row r="3" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>138</v>
+      </c>
       <c r="B3" s="3" t="s">
         <v>18</v>
       </c>
@@ -870,11 +894,19 @@
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
+    <row r="4" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>138</v>
+      </c>
       <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
@@ -897,11 +929,19 @@
         <v>29</v>
       </c>
       <c r="I4" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
+    <row r="5" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>138</v>
+      </c>
       <c r="B5" s="3" t="s">
         <v>30</v>
       </c>
@@ -924,10 +964,16 @@
         <v>34</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="69" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>35</v>
       </c>
@@ -952,12 +998,20 @@
       <c r="H6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
+    <row r="7" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="B7" s="5" t="s">
         <v>43</v>
       </c>
@@ -979,12 +1033,20 @@
       <c r="H7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
+    <row r="8" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="B8" s="5" t="s">
         <v>49</v>
       </c>
@@ -1006,12 +1068,20 @@
       <c r="H8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
+    <row r="9" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="B9" s="5" t="s">
         <v>56</v>
       </c>
@@ -1033,12 +1103,20 @@
       <c r="H9" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
+    <row r="10" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="B10" s="5" t="s">
         <v>62</v>
       </c>
@@ -1060,12 +1138,20 @@
       <c r="H10" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
+    <row r="11" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="B11" s="5" t="s">
         <v>67</v>
       </c>
@@ -1087,12 +1173,20 @@
       <c r="H11" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
+    <row r="12" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="B12" s="5" t="s">
         <v>73</v>
       </c>
@@ -1114,11 +1208,17 @@
       <c r="H12" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K12" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="69" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>79</v>
       </c>
@@ -1143,12 +1243,20 @@
       <c r="H13" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
+    <row r="14" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
+        <v>138</v>
+      </c>
       <c r="B14" s="5" t="s">
         <v>85</v>
       </c>
@@ -1170,11 +1278,17 @@
       <c r="H14" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K14" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>90</v>
       </c>
@@ -1199,12 +1313,20 @@
       <c r="H15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K15" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
+    <row r="16" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="B16" s="5" t="s">
         <v>96</v>
       </c>
@@ -1220,12 +1342,26 @@
       <c r="F16" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-    </row>
-    <row r="17" spans="1:9" ht="124.2" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
+      <c r="G16" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="B17" s="5" t="s">
         <v>138</v>
       </c>
@@ -1247,11 +1383,17 @@
       <c r="H17" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K17" s="10" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="165.6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>107</v>
       </c>
@@ -1276,11 +1418,17 @@
       <c r="H18" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K18" s="10" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="124.2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>112</v>
       </c>
@@ -1305,11 +1453,17 @@
       <c r="H19" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K19" s="10" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
         <v>113</v>
       </c>
@@ -1334,12 +1488,20 @@
       <c r="H20" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K20" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
+    <row r="21" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="B21" s="5" t="s">
         <v>118</v>
       </c>
@@ -1355,11 +1517,23 @@
       <c r="F21" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-    </row>
-    <row r="22" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="G21" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>122</v>
       </c>
@@ -1384,12 +1558,20 @@
       <c r="H22" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K22" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
+    <row r="23" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="B23" s="5" t="s">
         <v>128</v>
       </c>
@@ -1405,11 +1587,23 @@
       <c r="F23" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-    </row>
-    <row r="24" spans="1:9" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="G23" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="57" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>132</v>
       </c>
@@ -1434,22 +1628,17 @@
       <c r="H24" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K24" s="10" t="s">
         <v>106</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="A6:A12"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A13:A14"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>